--- a/Excel/BabelMythConfig.xlsx
+++ b/Excel/BabelMythConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -105,40 +105,49 @@
     <t>1000,100,1,1</t>
   </si>
   <si>
-    <t>1,5,20,50</t>
+    <t>1,5,10,50</t>
   </si>
   <si>
     <t>1 宠物口粮，5 改造石，20 时装精华 50 金色魂心</t>
   </si>
   <si>
+    <t>2000,150,1,1</t>
+  </si>
+  <si>
     <t>5,5,5,5,5</t>
   </si>
   <si>
     <t>4022,4021,4034,4025,4041</t>
   </si>
   <si>
-    <t>2000,200,1,1,1</t>
-  </si>
-  <si>
-    <t>1,5,20,50,100</t>
+    <t>3000,200,1,1,1</t>
+  </si>
+  <si>
+    <t>1,5,10,40,80</t>
   </si>
   <si>
     <t>1 宠物口粮，5 改造石，20 时装精华 50 金色魂心 100 暗金魂心</t>
   </si>
   <si>
+    <t>4000,250,1,1,1</t>
+  </si>
+  <si>
     <t>5,5,5,5,5,5</t>
   </si>
   <si>
     <t>4022,4021,4034,4025,4041,4053</t>
   </si>
   <si>
-    <t>3000,300,1,1,1,1</t>
-  </si>
-  <si>
-    <t>1,5,20,50,100,150</t>
+    <t>5000,300,1,1,1,1</t>
+  </si>
+  <si>
+    <t>1,5,10,30,60,100</t>
   </si>
   <si>
     <t>1 宠物口粮，5 改造石，20 时装精华 50 金色魂心 100 暗金魂心 150暗金兽魂</t>
+  </si>
+  <si>
+    <t>6000,350,1,1,1,1</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1255,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>11</v>
@@ -1278,26 +1287,27 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f>E6+1</f>
-        <v>1001</v>
+        <f t="shared" ref="D7:D11" si="0">D6+500</f>
+        <v>501</v>
       </c>
       <c r="E7" s="1">
-        <v>2000</v>
+        <f t="shared" ref="E7:E11" si="1">E6+500</f>
+        <v>1000</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1305,49 +1315,127 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f>E7+1</f>
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>1501</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>2501</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1"/>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1"/>
+      <c r="H11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="G12" s="6"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1"/>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="G14" s="6"/>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="F21" s="6"/>
-    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" customHeight="1"/>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="F22" s="6"/>
     </row>
@@ -1372,47 +1460,35 @@
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="F29" s="6"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:11">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="8"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:9">
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="8"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="3:9">
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -1421,7 +1497,7 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="3:9">
+    <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -1430,45 +1506,63 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="3:9">
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="7"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="3:9">
+    <row r="37" customHeight="1" spans="3:11">
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="7"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="3:9">
+    <row r="38" customHeight="1" spans="3:11">
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="3:9">
+    <row r="39" customHeight="1" spans="3:11">
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="3:9">
+    <row r="40" customHeight="1" spans="3:11">
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="3:9">
+    <row r="41" customHeight="1" spans="3:11">
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="3:9">
+    <row r="42" customHeight="1" spans="3:11">
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="3:9">
+    <row r="43" customHeight="1" spans="3:11">
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="3:9">
+    <row r="44" customHeight="1" spans="3:11">
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
+    <row r="45" customHeight="1" spans="3:11">
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H3 I3 C4:E4 F4 G4:H4 I4 C5:H5 I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
